--- a/StructureDefinition-access-unalign-out.xlsx
+++ b/StructureDefinition-access-unalign-out.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T23:16:42-05:00</t>
+    <t>2026-03-06T16:03:26-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -532,7 +532,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSUnalignmentResultVS|0.7.0</t>
+    <t>https://globalalliantinc.com/access/ValueSet/ACCESSUnalignmentResultVS|0.9.0</t>
   </si>
   <si>
     <t>Parameters.parameter:result.resource</t>

--- a/StructureDefinition-access-unalign-out.xlsx
+++ b/StructureDefinition-access-unalign-out.xlsx
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/StructureDefinition/access-unalign-out</t>
+    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-unalign-out</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T16:03:26-05:00</t>
+    <t>2026-03-12T23:55:37-07:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -532,7 +532,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/ValueSet/ACCESSUnalignmentResultVS|0.9.0</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentResultVS|0.9.1</t>
   </si>
   <si>
     <t>Parameters.parameter:result.resource</t>
@@ -883,7 +883,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.2890625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.87109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-access-unalign-out.xlsx
+++ b/StructureDefinition-access-unalign-out.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="167">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T23:55:37-07:00</t>
+    <t>2026-04-24T13:45:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -351,9 +351,6 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
@@ -532,7 +529,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentResultVS|0.9.1</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentResultVS|0.9.6</t>
   </si>
   <si>
     <t>Parameters.parameter:result.resource</t>
@@ -1508,29 +1505,27 @@
       <c r="X6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Y6" s="2"/>
+      <c r="Z6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -1553,10 +1548,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1579,13 +1574,13 @@
         <v>85</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1624,17 +1619,17 @@
         <v>75</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AC7" s="2"/>
       <c r="AD7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -1646,7 +1641,7 @@
         <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
@@ -1657,10 +1652,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1683,13 +1678,13 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1740,7 +1735,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -1763,14 +1758,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1789,16 +1784,16 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1848,7 +1843,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -1860,7 +1855,7 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
@@ -1871,14 +1866,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -1897,19 +1892,19 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>75</v>
@@ -1958,7 +1953,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -1970,21 +1965,21 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2007,13 +2002,13 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2064,7 +2059,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>84</v>
@@ -2087,10 +2082,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2113,13 +2108,13 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2170,7 +2165,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2179,7 +2174,7 @@
         <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
@@ -2193,10 +2188,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2219,16 +2214,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2278,7 +2273,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2287,7 +2282,7 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>75</v>
@@ -2301,10 +2296,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2330,13 +2325,13 @@
         <v>75</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2386,7 +2381,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2409,13 +2404,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>75</v>
@@ -2437,13 +2432,13 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2494,7 +2489,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2506,7 +2501,7 @@
         <v>75</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
@@ -2517,10 +2512,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2543,13 +2538,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2600,7 +2595,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2623,14 +2618,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2649,16 +2644,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2708,7 +2703,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -2720,7 +2715,7 @@
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
@@ -2731,14 +2726,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -2757,19 +2752,19 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="O18" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -2818,7 +2813,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -2830,21 +2825,21 @@
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2867,13 +2862,13 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2882,7 +2877,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>75</v>
@@ -2924,7 +2919,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -2947,10 +2942,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2973,13 +2968,13 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3006,11 +3001,11 @@
         <v>75</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>75</v>
@@ -3028,7 +3023,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3037,7 +3032,7 @@
         <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>96</v>
@@ -3051,10 +3046,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3077,16 +3072,16 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3136,7 +3131,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3145,7 +3140,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>75</v>
@@ -3159,10 +3154,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3188,13 +3183,13 @@
         <v>78</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3244,7 +3239,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>

--- a/StructureDefinition-access-unalign-out.xlsx
+++ b/StructureDefinition-access-unalign-out.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -529,7 +529,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentResultVS|0.9.6</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentResultVS|0.9.8</t>
   </si>
   <si>
     <t>Parameters.parameter:result.resource</t>

--- a/StructureDefinition-access-unalign-out.xlsx
+++ b/StructureDefinition-access-unalign-out.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-unalign-out.xlsx
+++ b/StructureDefinition-access-unalign-out.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -529,7 +529,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentResultVS|0.9.8</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentResultVS|0.9.11</t>
   </si>
   <si>
     <t>Parameters.parameter:result.resource</t>
@@ -880,7 +880,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.87109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="72.87109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-access-unalign-out.xlsx
+++ b/StructureDefinition-access-unalign-out.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-unalign-out.xlsx
+++ b/StructureDefinition-access-unalign-out.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -529,7 +529,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentResultVS|0.9.11</t>
+    <t>https://dsacms.github.io/cmmi-access-model/ValueSet/ACCESSUnalignmentResultVS|0.9.12</t>
   </si>
   <si>
     <t>Parameters.parameter:result.resource</t>
